--- a/data/usa/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/usa/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL362"/>
+  <dimension ref="A1:BL365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74117,15 +74117,11 @@
           <t>23 188</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G347" t="n">
+        <v>0</v>
+      </c>
+      <c r="H347" t="n">
+        <v>0</v>
       </c>
       <c r="I347" t="inlineStr">
         <is>
@@ -74157,175 +74153,107 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="O347" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="P347" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q347" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R347" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S347" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T347" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U347" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V347" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W347" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X347" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y347" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z347" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA347" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB347" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC347" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AD347" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AE347" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF347" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG347" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH347" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI347" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ347" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK347" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="AL347" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="AM347" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="AN347" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="AO347" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="AP347" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AQ347" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AR347" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AS347" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AT347" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AU347" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AV347" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="O347" t="n">
+        <v>15</v>
+      </c>
+      <c r="P347" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>5</v>
+      </c>
+      <c r="R347" t="n">
+        <v>2</v>
+      </c>
+      <c r="S347" t="n">
+        <v>3</v>
+      </c>
+      <c r="T347" t="n">
+        <v>2</v>
+      </c>
+      <c r="U347" t="n">
+        <v>7</v>
+      </c>
+      <c r="V347" t="n">
+        <v>1</v>
+      </c>
+      <c r="W347" t="n">
+        <v>10</v>
+      </c>
+      <c r="X347" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA347" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB347" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC347" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD347" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE347" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF347" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG347" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH347" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI347" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ347" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK347" t="n">
+        <v>560</v>
+      </c>
+      <c r="AL347" t="n">
+        <v>532</v>
+      </c>
+      <c r="AM347" t="n">
+        <v>493</v>
+      </c>
+      <c r="AN347" t="n">
+        <v>449</v>
+      </c>
+      <c r="AO347" t="n">
+        <v>131</v>
+      </c>
+      <c r="AP347" t="n">
+        <v>77</v>
+      </c>
+      <c r="AQ347" t="n">
+        <v>59</v>
+      </c>
+      <c r="AR347" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS347" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT347" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU347" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV347" t="n">
+        <v>2</v>
       </c>
       <c r="AW347" t="inlineStr">
         <is>
@@ -74356,10 +74284,8 @@
       <c r="BC347" t="n">
         <v>0</v>
       </c>
-      <c r="BD347" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD347" t="n">
+        <v>2024</v>
       </c>
       <c r="BE347" t="inlineStr"/>
       <c r="BF347" t="inlineStr"/>
@@ -74403,15 +74329,11 @@
           <t>16 426</t>
         </is>
       </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G348" t="n">
+        <v>1</v>
+      </c>
+      <c r="H348" t="n">
+        <v>2</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>
@@ -74443,175 +74365,107 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="O348" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P348" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Q348" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R348" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S348" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T348" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U348" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V348" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W348" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X348" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y348" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z348" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA348" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB348" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC348" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AD348" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AE348" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF348" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG348" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH348" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI348" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ348" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK348" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="AL348" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="AM348" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="AN348" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="AO348" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="AP348" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AQ348" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AR348" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AS348" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AT348" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AU348" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AV348" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O348" t="n">
+        <v>5</v>
+      </c>
+      <c r="P348" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>2</v>
+      </c>
+      <c r="R348" t="n">
+        <v>3</v>
+      </c>
+      <c r="S348" t="n">
+        <v>2</v>
+      </c>
+      <c r="T348" t="n">
+        <v>3</v>
+      </c>
+      <c r="U348" t="n">
+        <v>1</v>
+      </c>
+      <c r="V348" t="n">
+        <v>3</v>
+      </c>
+      <c r="W348" t="n">
+        <v>15</v>
+      </c>
+      <c r="X348" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC348" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD348" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG348" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH348" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ348" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK348" t="n">
+        <v>690</v>
+      </c>
+      <c r="AL348" t="n">
+        <v>353</v>
+      </c>
+      <c r="AM348" t="n">
+        <v>608</v>
+      </c>
+      <c r="AN348" t="n">
+        <v>278</v>
+      </c>
+      <c r="AO348" t="n">
+        <v>146</v>
+      </c>
+      <c r="AP348" t="n">
+        <v>98</v>
+      </c>
+      <c r="AQ348" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR348" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS348" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT348" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU348" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV348" t="n">
+        <v>1</v>
       </c>
       <c r="AW348" t="inlineStr">
         <is>
@@ -74642,10 +74496,8 @@
       <c r="BC348" t="n">
         <v>0</v>
       </c>
-      <c r="BD348" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD348" t="n">
+        <v>2024</v>
       </c>
       <c r="BE348" t="inlineStr"/>
       <c r="BF348" t="inlineStr"/>
@@ -74685,15 +74537,11 @@
         </is>
       </c>
       <c r="F349" t="inlineStr"/>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G349" t="n">
+        <v>0</v>
+      </c>
+      <c r="H349" t="n">
+        <v>0</v>
       </c>
       <c r="I349" t="inlineStr">
         <is>
@@ -74725,175 +74573,107 @@
           <t>37%</t>
         </is>
       </c>
-      <c r="O349" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P349" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q349" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R349" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S349" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T349" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U349" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V349" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W349" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X349" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y349" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z349" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA349" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB349" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC349" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AD349" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE349" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF349" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG349" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH349" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AI349" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ349" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK349" t="inlineStr">
-        <is>
-          <t>728</t>
-        </is>
-      </c>
-      <c r="AL349" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="AM349" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="AN349" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="AO349" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AP349" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AQ349" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AR349" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AS349" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AT349" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AU349" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AV349" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="O349" t="n">
+        <v>11</v>
+      </c>
+      <c r="P349" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>4</v>
+      </c>
+      <c r="R349" t="n">
+        <v>2</v>
+      </c>
+      <c r="S349" t="n">
+        <v>5</v>
+      </c>
+      <c r="T349" t="n">
+        <v>4</v>
+      </c>
+      <c r="U349" t="n">
+        <v>2</v>
+      </c>
+      <c r="V349" t="n">
+        <v>2</v>
+      </c>
+      <c r="W349" t="n">
+        <v>15</v>
+      </c>
+      <c r="X349" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z349" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA349" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB349" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC349" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD349" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE349" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF349" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG349" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH349" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI349" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ349" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK349" t="n">
+        <v>728</v>
+      </c>
+      <c r="AL349" t="n">
+        <v>407</v>
+      </c>
+      <c r="AM349" t="n">
+        <v>657</v>
+      </c>
+      <c r="AN349" t="n">
+        <v>344</v>
+      </c>
+      <c r="AO349" t="n">
+        <v>142</v>
+      </c>
+      <c r="AP349" t="n">
+        <v>74</v>
+      </c>
+      <c r="AQ349" t="n">
+        <v>59</v>
+      </c>
+      <c r="AR349" t="n">
+        <v>37</v>
+      </c>
+      <c r="AS349" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT349" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU349" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV349" t="n">
+        <v>2</v>
       </c>
       <c r="AW349" t="inlineStr">
         <is>
@@ -74924,10 +74704,8 @@
       <c r="BC349" t="n">
         <v>0</v>
       </c>
-      <c r="BD349" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD349" t="n">
+        <v>2024</v>
       </c>
       <c r="BE349" t="inlineStr"/>
       <c r="BF349" t="inlineStr"/>
@@ -74971,15 +74749,11 @@
           <t>20 523</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G350" t="n">
+        <v>0</v>
+      </c>
+      <c r="H350" t="n">
+        <v>4</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
@@ -75011,175 +74785,107 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="O350" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P350" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q350" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R350" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S350" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T350" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U350" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V350" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W350" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X350" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y350" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z350" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA350" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB350" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC350" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AD350" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AE350" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF350" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG350" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH350" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI350" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ350" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK350" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="AL350" t="inlineStr">
-        <is>
-          <t>556</t>
-        </is>
-      </c>
-      <c r="AM350" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="AN350" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="AO350" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="AP350" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AQ350" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="AR350" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AS350" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AT350" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AU350" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AV350" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O350" t="n">
+        <v>10</v>
+      </c>
+      <c r="P350" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>1</v>
+      </c>
+      <c r="R350" t="n">
+        <v>8</v>
+      </c>
+      <c r="S350" t="n">
+        <v>7</v>
+      </c>
+      <c r="T350" t="n">
+        <v>4</v>
+      </c>
+      <c r="U350" t="n">
+        <v>2</v>
+      </c>
+      <c r="V350" t="n">
+        <v>3</v>
+      </c>
+      <c r="W350" t="n">
+        <v>10</v>
+      </c>
+      <c r="X350" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z350" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA350" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB350" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC350" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD350" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE350" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG350" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH350" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI350" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK350" t="n">
+        <v>652</v>
+      </c>
+      <c r="AL350" t="n">
+        <v>556</v>
+      </c>
+      <c r="AM350" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN350" t="n">
+        <v>490</v>
+      </c>
+      <c r="AO350" t="n">
+        <v>145</v>
+      </c>
+      <c r="AP350" t="n">
+        <v>98</v>
+      </c>
+      <c r="AQ350" t="n">
+        <v>65</v>
+      </c>
+      <c r="AR350" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS350" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT350" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU350" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV350" t="n">
+        <v>1</v>
       </c>
       <c r="AW350" t="inlineStr">
         <is>
@@ -75210,20 +74916,14 @@
       <c r="BC350" t="n">
         <v>0</v>
       </c>
-      <c r="BD350" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="BE350" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF350" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BD350" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BE350" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF350" t="n">
+        <v>0</v>
       </c>
       <c r="BG350" t="inlineStr"/>
       <c r="BH350" t="inlineStr"/>
@@ -75265,15 +74965,11 @@
           <t>30 512</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G351" t="n">
+        <v>2</v>
+      </c>
+      <c r="H351" t="n">
+        <v>2</v>
       </c>
       <c r="I351" t="inlineStr">
         <is>
@@ -75305,175 +75001,107 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="O351" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P351" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Q351" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R351" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S351" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T351" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U351" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V351" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W351" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X351" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y351" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z351" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA351" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB351" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC351" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AD351" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AE351" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF351" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG351" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH351" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI351" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ351" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK351" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="AL351" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="AM351" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
-      </c>
-      <c r="AN351" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="AO351" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AP351" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="AQ351" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AR351" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="AS351" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AT351" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AU351" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AV351" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="O351" t="n">
+        <v>10</v>
+      </c>
+      <c r="P351" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>4</v>
+      </c>
+      <c r="R351" t="n">
+        <v>13</v>
+      </c>
+      <c r="S351" t="n">
+        <v>3</v>
+      </c>
+      <c r="T351" t="n">
+        <v>5</v>
+      </c>
+      <c r="U351" t="n">
+        <v>3</v>
+      </c>
+      <c r="V351" t="n">
+        <v>6</v>
+      </c>
+      <c r="W351" t="n">
+        <v>11</v>
+      </c>
+      <c r="X351" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z351" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA351" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC351" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD351" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE351" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF351" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG351" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH351" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI351" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ351" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK351" t="n">
+        <v>521</v>
+      </c>
+      <c r="AL351" t="n">
+        <v>434</v>
+      </c>
+      <c r="AM351" t="n">
+        <v>439</v>
+      </c>
+      <c r="AN351" t="n">
+        <v>360</v>
+      </c>
+      <c r="AO351" t="n">
+        <v>116</v>
+      </c>
+      <c r="AP351" t="n">
+        <v>121</v>
+      </c>
+      <c r="AQ351" t="n">
+        <v>50</v>
+      </c>
+      <c r="AR351" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS351" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT351" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU351" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV351" t="n">
+        <v>0</v>
       </c>
       <c r="AW351" t="inlineStr">
         <is>
@@ -75504,10 +75132,8 @@
       <c r="BC351" t="n">
         <v>0</v>
       </c>
-      <c r="BD351" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD351" t="n">
+        <v>2024</v>
       </c>
       <c r="BE351" t="inlineStr"/>
       <c r="BF351" t="inlineStr"/>
@@ -75551,15 +75177,11 @@
           <t>17 708</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G352" t="n">
+        <v>1</v>
+      </c>
+      <c r="H352" t="n">
+        <v>1</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>
@@ -75591,175 +75213,107 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="O352" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P352" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q352" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R352" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S352" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T352" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U352" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V352" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W352" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="X352" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Y352" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z352" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA352" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB352" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC352" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AD352" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE352" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF352" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG352" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH352" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AI352" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ352" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK352" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="AL352" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="AM352" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="AN352" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="AO352" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="AP352" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="AQ352" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="AR352" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AS352" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AT352" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AU352" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV352" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="O352" t="n">
+        <v>10</v>
+      </c>
+      <c r="P352" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>3</v>
+      </c>
+      <c r="R352" t="n">
+        <v>1</v>
+      </c>
+      <c r="S352" t="n">
+        <v>6</v>
+      </c>
+      <c r="T352" t="n">
+        <v>1</v>
+      </c>
+      <c r="U352" t="n">
+        <v>1</v>
+      </c>
+      <c r="V352" t="n">
+        <v>2</v>
+      </c>
+      <c r="W352" t="n">
+        <v>22</v>
+      </c>
+      <c r="X352" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y352" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z352" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB352" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC352" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD352" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE352" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF352" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG352" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH352" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI352" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ352" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK352" t="n">
+        <v>576</v>
+      </c>
+      <c r="AL352" t="n">
+        <v>411</v>
+      </c>
+      <c r="AM352" t="n">
+        <v>475</v>
+      </c>
+      <c r="AN352" t="n">
+        <v>308</v>
+      </c>
+      <c r="AO352" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP352" t="n">
+        <v>94</v>
+      </c>
+      <c r="AQ352" t="n">
+        <v>57</v>
+      </c>
+      <c r="AR352" t="n">
+        <v>51</v>
+      </c>
+      <c r="AS352" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT352" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU352" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV352" t="n">
+        <v>0</v>
       </c>
       <c r="AW352" t="inlineStr">
         <is>
@@ -75790,20 +75344,14 @@
       <c r="BC352" t="n">
         <v>0</v>
       </c>
-      <c r="BD352" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="BE352" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF352" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BD352" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BE352" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF352" t="n">
+        <v>1</v>
       </c>
       <c r="BG352" t="inlineStr"/>
       <c r="BH352" t="inlineStr"/>
@@ -75845,15 +75393,11 @@
           <t>3 827</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G353" t="n">
+        <v>0</v>
+      </c>
+      <c r="H353" t="n">
+        <v>1</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
@@ -75885,159 +75429,99 @@
           <t>34%</t>
         </is>
       </c>
-      <c r="O353" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="P353" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q353" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R353" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S353" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="T353" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U353" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V353" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="O353" t="n">
+        <v>14</v>
+      </c>
+      <c r="P353" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>0</v>
+      </c>
+      <c r="R353" t="n">
+        <v>3</v>
+      </c>
+      <c r="S353" t="n">
+        <v>11</v>
+      </c>
+      <c r="T353" t="n">
+        <v>1</v>
+      </c>
+      <c r="U353" t="n">
+        <v>3</v>
+      </c>
+      <c r="V353" t="n">
+        <v>0</v>
       </c>
       <c r="W353" t="inlineStr"/>
       <c r="X353" t="inlineStr"/>
-      <c r="Y353" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z353" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA353" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB353" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y353" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA353" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB353" t="n">
+        <v>2</v>
       </c>
       <c r="AC353" t="inlineStr"/>
       <c r="AD353" t="inlineStr"/>
-      <c r="AE353" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF353" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG353" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH353" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI353" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ353" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK353" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="AL353" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="AM353" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="AN353" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="AO353" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AP353" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AQ353" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AR353" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AS353" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AT353" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="AU353" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AV353" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AE353" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF353" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG353" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH353" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI353" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ353" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK353" t="n">
+        <v>578</v>
+      </c>
+      <c r="AL353" t="n">
+        <v>337</v>
+      </c>
+      <c r="AM353" t="n">
+        <v>485</v>
+      </c>
+      <c r="AN353" t="n">
+        <v>245</v>
+      </c>
+      <c r="AO353" t="n">
+        <v>69</v>
+      </c>
+      <c r="AP353" t="n">
+        <v>56</v>
+      </c>
+      <c r="AQ353" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR353" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS353" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT353" t="n">
+        <v>41</v>
+      </c>
+      <c r="AU353" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV353" t="n">
+        <v>3</v>
       </c>
       <c r="AW353" t="inlineStr">
         <is>
@@ -76068,32 +75552,22 @@
       <c r="BC353" t="n">
         <v>0</v>
       </c>
-      <c r="BD353" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD353" t="n">
+        <v>2024</v>
       </c>
       <c r="BE353" t="inlineStr"/>
       <c r="BF353" t="inlineStr"/>
-      <c r="BG353" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BH353" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BI353" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BJ353" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="BG353" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH353" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI353" t="n">
+        <v>12</v>
+      </c>
+      <c r="BJ353" t="n">
+        <v>11</v>
       </c>
       <c r="BK353" t="inlineStr"/>
       <c r="BL353" t="inlineStr"/>
@@ -76131,15 +75605,11 @@
           <t>7 362</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G354" t="n">
+        <v>4</v>
+      </c>
+      <c r="H354" t="n">
+        <v>2</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
@@ -76171,159 +75641,99 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="O354" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P354" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Q354" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R354" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S354" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T354" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U354" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V354" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="O354" t="n">
+        <v>20</v>
+      </c>
+      <c r="P354" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>10</v>
+      </c>
+      <c r="R354" t="n">
+        <v>4</v>
+      </c>
+      <c r="S354" t="n">
+        <v>4</v>
+      </c>
+      <c r="T354" t="n">
+        <v>10</v>
+      </c>
+      <c r="U354" t="n">
+        <v>6</v>
+      </c>
+      <c r="V354" t="n">
+        <v>5</v>
       </c>
       <c r="W354" t="inlineStr"/>
       <c r="X354" t="inlineStr"/>
-      <c r="Y354" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z354" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA354" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB354" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y354" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA354" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB354" t="n">
+        <v>4</v>
       </c>
       <c r="AC354" t="inlineStr"/>
       <c r="AD354" t="inlineStr"/>
-      <c r="AE354" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF354" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG354" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH354" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI354" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ354" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK354" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="AL354" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="AM354" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="AN354" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="AO354" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AP354" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AQ354" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="AR354" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="AS354" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AT354" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AU354" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AV354" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="AE354" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF354" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG354" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH354" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI354" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ354" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK354" t="n">
+        <v>410</v>
+      </c>
+      <c r="AL354" t="n">
+        <v>390</v>
+      </c>
+      <c r="AM354" t="n">
+        <v>338</v>
+      </c>
+      <c r="AN354" t="n">
+        <v>314</v>
+      </c>
+      <c r="AO354" t="n">
+        <v>111</v>
+      </c>
+      <c r="AP354" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ354" t="n">
+        <v>57</v>
+      </c>
+      <c r="AR354" t="n">
+        <v>65</v>
+      </c>
+      <c r="AS354" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT354" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU354" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV354" t="n">
+        <v>8</v>
       </c>
       <c r="AW354" t="inlineStr">
         <is>
@@ -76354,32 +75764,22 @@
       <c r="BC354" t="n">
         <v>0</v>
       </c>
-      <c r="BD354" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD354" t="n">
+        <v>2024</v>
       </c>
       <c r="BE354" t="inlineStr"/>
       <c r="BF354" t="inlineStr"/>
-      <c r="BG354" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BH354" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BI354" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BJ354" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BG354" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH354" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI354" t="n">
+        <v>13</v>
+      </c>
+      <c r="BJ354" t="n">
+        <v>6</v>
       </c>
       <c r="BK354" t="inlineStr"/>
       <c r="BL354" t="inlineStr"/>
@@ -76417,15 +75817,11 @@
           <t>5 764</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G355" t="n">
+        <v>0</v>
+      </c>
+      <c r="H355" t="n">
+        <v>0</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
@@ -76457,159 +75853,99 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="O355" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P355" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Q355" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S355" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="O355" t="n">
+        <v>5</v>
+      </c>
+      <c r="P355" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>2</v>
+      </c>
+      <c r="R355" t="n">
+        <v>3</v>
+      </c>
+      <c r="S355" t="n">
+        <v>0</v>
+      </c>
+      <c r="T355" t="n">
+        <v>3</v>
+      </c>
+      <c r="U355" t="n">
+        <v>3</v>
+      </c>
+      <c r="V355" t="n">
+        <v>3</v>
       </c>
       <c r="W355" t="inlineStr"/>
       <c r="X355" t="inlineStr"/>
-      <c r="Y355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA355" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB355" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y355" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA355" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB355" t="n">
+        <v>2</v>
       </c>
       <c r="AC355" t="inlineStr"/>
       <c r="AD355" t="inlineStr"/>
-      <c r="AE355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF355" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG355" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH355" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AI355" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ355" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK355" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="AL355" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="AM355" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="AN355" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="AO355" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AP355" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="AQ355" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AR355" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AS355" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AT355" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AU355" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AV355" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AE355" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF355" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG355" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH355" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI355" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ355" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK355" t="n">
+        <v>589</v>
+      </c>
+      <c r="AL355" t="n">
+        <v>405</v>
+      </c>
+      <c r="AM355" t="n">
+        <v>506</v>
+      </c>
+      <c r="AN355" t="n">
+        <v>321</v>
+      </c>
+      <c r="AO355" t="n">
+        <v>113</v>
+      </c>
+      <c r="AP355" t="n">
+        <v>94</v>
+      </c>
+      <c r="AQ355" t="n">
+        <v>71</v>
+      </c>
+      <c r="AR355" t="n">
+        <v>76</v>
+      </c>
+      <c r="AS355" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT355" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU355" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV355" t="n">
+        <v>2</v>
       </c>
       <c r="AW355" t="inlineStr">
         <is>
@@ -76640,32 +75976,22 @@
       <c r="BC355" t="n">
         <v>0</v>
       </c>
-      <c r="BD355" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD355" t="n">
+        <v>2024</v>
       </c>
       <c r="BE355" t="inlineStr"/>
       <c r="BF355" t="inlineStr"/>
-      <c r="BG355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BH355" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BI355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BJ355" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BG355" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH355" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI355" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ355" t="n">
+        <v>8</v>
       </c>
       <c r="BK355" t="inlineStr"/>
       <c r="BL355" t="inlineStr"/>
@@ -76703,15 +76029,11 @@
           <t>3 525</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G356" t="n">
+        <v>2</v>
+      </c>
+      <c r="H356" t="n">
+        <v>1</v>
       </c>
       <c r="I356" t="inlineStr">
         <is>
@@ -76743,159 +76065,99 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="O356" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="P356" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q356" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R356" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S356" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T356" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U356" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V356" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O356" t="n">
+        <v>14</v>
+      </c>
+      <c r="P356" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>5</v>
+      </c>
+      <c r="R356" t="n">
+        <v>3</v>
+      </c>
+      <c r="S356" t="n">
+        <v>5</v>
+      </c>
+      <c r="T356" t="n">
+        <v>7</v>
+      </c>
+      <c r="U356" t="n">
+        <v>4</v>
+      </c>
+      <c r="V356" t="n">
+        <v>1</v>
       </c>
       <c r="W356" t="inlineStr"/>
       <c r="X356" t="inlineStr"/>
-      <c r="Y356" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z356" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA356" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB356" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y356" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA356" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB356" t="n">
+        <v>0</v>
       </c>
       <c r="AC356" t="inlineStr"/>
       <c r="AD356" t="inlineStr"/>
-      <c r="AE356" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF356" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG356" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH356" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI356" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ356" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK356" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="AL356" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="AM356" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="AN356" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AO356" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AP356" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AQ356" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="AR356" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AS356" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AT356" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AU356" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AV356" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AE356" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF356" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG356" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH356" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI356" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ356" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK356" t="n">
+        <v>655</v>
+      </c>
+      <c r="AL356" t="n">
+        <v>390</v>
+      </c>
+      <c r="AM356" t="n">
+        <v>544</v>
+      </c>
+      <c r="AN356" t="n">
+        <v>281</v>
+      </c>
+      <c r="AO356" t="n">
+        <v>96</v>
+      </c>
+      <c r="AP356" t="n">
+        <v>77</v>
+      </c>
+      <c r="AQ356" t="n">
+        <v>62</v>
+      </c>
+      <c r="AR356" t="n">
+        <v>31</v>
+      </c>
+      <c r="AS356" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT356" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU356" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV356" t="n">
+        <v>4</v>
       </c>
       <c r="AW356" t="inlineStr">
         <is>
@@ -76926,32 +76188,22 @@
       <c r="BC356" t="n">
         <v>0</v>
       </c>
-      <c r="BD356" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD356" t="n">
+        <v>2024</v>
       </c>
       <c r="BE356" t="inlineStr"/>
       <c r="BF356" t="inlineStr"/>
-      <c r="BG356" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BH356" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BI356" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BJ356" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="BG356" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH356" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI356" t="n">
+        <v>21</v>
+      </c>
+      <c r="BJ356" t="n">
+        <v>12</v>
       </c>
       <c r="BK356" t="inlineStr"/>
       <c r="BL356" t="inlineStr"/>
@@ -76985,15 +76237,11 @@
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G357" t="n">
+        <v>5</v>
+      </c>
+      <c r="H357" t="n">
+        <v>0</v>
       </c>
       <c r="I357" t="inlineStr">
         <is>
@@ -77025,159 +76273,99 @@
           <t>56%</t>
         </is>
       </c>
-      <c r="O357" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="P357" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Q357" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R357" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S357" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="T357" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U357" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V357" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="O357" t="n">
+        <v>23</v>
+      </c>
+      <c r="P357" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>9</v>
+      </c>
+      <c r="R357" t="n">
+        <v>3</v>
+      </c>
+      <c r="S357" t="n">
+        <v>13</v>
+      </c>
+      <c r="T357" t="n">
+        <v>6</v>
+      </c>
+      <c r="U357" t="n">
+        <v>1</v>
+      </c>
+      <c r="V357" t="n">
+        <v>0</v>
       </c>
       <c r="W357" t="inlineStr"/>
       <c r="X357" t="inlineStr"/>
-      <c r="Y357" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z357" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA357" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB357" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y357" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA357" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB357" t="n">
+        <v>5</v>
       </c>
       <c r="AC357" t="inlineStr"/>
       <c r="AD357" t="inlineStr"/>
-      <c r="AE357" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF357" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG357" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AH357" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AI357" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ357" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK357" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="AL357" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="AM357" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="AN357" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="AO357" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="AP357" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AQ357" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AR357" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AS357" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AT357" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AU357" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AV357" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AE357" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF357" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG357" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH357" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI357" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ357" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK357" t="n">
+        <v>404</v>
+      </c>
+      <c r="AL357" t="n">
+        <v>543</v>
+      </c>
+      <c r="AM357" t="n">
+        <v>319</v>
+      </c>
+      <c r="AN357" t="n">
+        <v>452</v>
+      </c>
+      <c r="AO357" t="n">
+        <v>101</v>
+      </c>
+      <c r="AP357" t="n">
+        <v>114</v>
+      </c>
+      <c r="AQ357" t="n">
+        <v>60</v>
+      </c>
+      <c r="AR357" t="n">
+        <v>49</v>
+      </c>
+      <c r="AS357" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT357" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU357" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV357" t="n">
+        <v>2</v>
       </c>
       <c r="AW357" t="inlineStr">
         <is>
@@ -77208,32 +76396,22 @@
       <c r="BC357" t="n">
         <v>0</v>
       </c>
-      <c r="BD357" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD357" t="n">
+        <v>2024</v>
       </c>
       <c r="BE357" t="inlineStr"/>
       <c r="BF357" t="inlineStr"/>
-      <c r="BG357" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BH357" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BI357" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BJ357" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="BG357" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH357" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI357" t="n">
+        <v>18</v>
+      </c>
+      <c r="BJ357" t="n">
+        <v>9</v>
       </c>
       <c r="BK357" t="inlineStr"/>
       <c r="BL357" t="inlineStr"/>
@@ -77267,15 +76445,11 @@
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G358" t="n">
+        <v>0</v>
+      </c>
+      <c r="H358" t="n">
+        <v>0</v>
       </c>
       <c r="I358" t="inlineStr">
         <is>
@@ -77307,159 +76481,99 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="O358" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P358" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q358" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R358" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S358" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T358" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U358" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V358" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="O358" t="n">
+        <v>8</v>
+      </c>
+      <c r="P358" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>0</v>
+      </c>
+      <c r="R358" t="n">
+        <v>2</v>
+      </c>
+      <c r="S358" t="n">
+        <v>7</v>
+      </c>
+      <c r="T358" t="n">
+        <v>2</v>
+      </c>
+      <c r="U358" t="n">
+        <v>1</v>
+      </c>
+      <c r="V358" t="n">
+        <v>6</v>
       </c>
       <c r="W358" t="inlineStr"/>
       <c r="X358" t="inlineStr"/>
-      <c r="Y358" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z358" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA358" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB358" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y358" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA358" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB358" t="n">
+        <v>2</v>
       </c>
       <c r="AC358" t="inlineStr"/>
       <c r="AD358" t="inlineStr"/>
-      <c r="AE358" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF358" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG358" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH358" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI358" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ358" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK358" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="AL358" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="AM358" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="AN358" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="AO358" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="AP358" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AQ358" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AR358" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AS358" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AT358" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AU358" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AV358" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AE358" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF358" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG358" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH358" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI358" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ358" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK358" t="n">
+        <v>456</v>
+      </c>
+      <c r="AL358" t="n">
+        <v>338</v>
+      </c>
+      <c r="AM358" t="n">
+        <v>373</v>
+      </c>
+      <c r="AN358" t="n">
+        <v>276</v>
+      </c>
+      <c r="AO358" t="n">
+        <v>73</v>
+      </c>
+      <c r="AP358" t="n">
+        <v>82</v>
+      </c>
+      <c r="AQ358" t="n">
+        <v>31</v>
+      </c>
+      <c r="AR358" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS358" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT358" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU358" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV358" t="n">
+        <v>1</v>
       </c>
       <c r="AW358" t="inlineStr">
         <is>
@@ -77490,32 +76604,22 @@
       <c r="BC358" t="n">
         <v>0</v>
       </c>
-      <c r="BD358" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD358" t="n">
+        <v>2024</v>
       </c>
       <c r="BE358" t="inlineStr"/>
       <c r="BF358" t="inlineStr"/>
-      <c r="BG358" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BH358" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BI358" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BJ358" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="BG358" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH358" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI358" t="n">
+        <v>16</v>
+      </c>
+      <c r="BJ358" t="n">
+        <v>7</v>
       </c>
       <c r="BK358" t="inlineStr"/>
       <c r="BL358" t="inlineStr"/>
@@ -77553,15 +76657,11 @@
           <t>5 619</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G359" t="n">
+        <v>2</v>
+      </c>
+      <c r="H359" t="n">
+        <v>0</v>
       </c>
       <c r="I359" t="inlineStr">
         <is>
@@ -77593,159 +76693,99 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="O359" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P359" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q359" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R359" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S359" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T359" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U359" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V359" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="O359" t="n">
+        <v>6</v>
+      </c>
+      <c r="P359" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>3</v>
+      </c>
+      <c r="R359" t="n">
+        <v>0</v>
+      </c>
+      <c r="S359" t="n">
+        <v>2</v>
+      </c>
+      <c r="T359" t="n">
+        <v>0</v>
+      </c>
+      <c r="U359" t="n">
+        <v>1</v>
+      </c>
+      <c r="V359" t="n">
+        <v>2</v>
       </c>
       <c r="W359" t="inlineStr"/>
       <c r="X359" t="inlineStr"/>
-      <c r="Y359" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z359" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA359" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB359" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y359" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA359" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB359" t="n">
+        <v>4</v>
       </c>
       <c r="AC359" t="inlineStr"/>
       <c r="AD359" t="inlineStr"/>
-      <c r="AE359" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF359" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG359" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH359" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI359" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ359" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK359" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="AL359" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="AM359" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="AN359" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AO359" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AP359" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="AQ359" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AR359" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AS359" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AT359" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AU359" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AV359" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AE359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF359" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG359" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH359" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI359" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ359" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK359" t="n">
+        <v>380</v>
+      </c>
+      <c r="AL359" t="n">
+        <v>650</v>
+      </c>
+      <c r="AM359" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN359" t="n">
+        <v>509</v>
+      </c>
+      <c r="AO359" t="n">
+        <v>84</v>
+      </c>
+      <c r="AP359" t="n">
+        <v>87</v>
+      </c>
+      <c r="AQ359" t="n">
+        <v>68</v>
+      </c>
+      <c r="AR359" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS359" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT359" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU359" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV359" t="n">
+        <v>1</v>
       </c>
       <c r="AW359" t="inlineStr">
         <is>
@@ -77776,32 +76816,22 @@
       <c r="BC359" t="n">
         <v>0</v>
       </c>
-      <c r="BD359" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD359" t="n">
+        <v>2024</v>
       </c>
       <c r="BE359" t="inlineStr"/>
       <c r="BF359" t="inlineStr"/>
-      <c r="BG359" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BH359" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BI359" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BJ359" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="BG359" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH359" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI359" t="n">
+        <v>16</v>
+      </c>
+      <c r="BJ359" t="n">
+        <v>15</v>
       </c>
       <c r="BK359" t="inlineStr"/>
       <c r="BL359" t="inlineStr"/>
@@ -77835,15 +76865,11 @@
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G360" t="n">
+        <v>1</v>
+      </c>
+      <c r="H360" t="n">
+        <v>0</v>
       </c>
       <c r="I360" t="inlineStr">
         <is>
@@ -77875,159 +76901,99 @@
           <t>30%</t>
         </is>
       </c>
-      <c r="O360" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P360" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q360" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R360" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S360" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T360" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U360" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V360" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="O360" t="n">
+        <v>6</v>
+      </c>
+      <c r="P360" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>3</v>
+      </c>
+      <c r="R360" t="n">
+        <v>0</v>
+      </c>
+      <c r="S360" t="n">
+        <v>2</v>
+      </c>
+      <c r="T360" t="n">
+        <v>0</v>
+      </c>
+      <c r="U360" t="n">
+        <v>1</v>
+      </c>
+      <c r="V360" t="n">
+        <v>0</v>
       </c>
       <c r="W360" t="inlineStr"/>
       <c r="X360" t="inlineStr"/>
-      <c r="Y360" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z360" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA360" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB360" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y360" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA360" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB360" t="n">
+        <v>2</v>
       </c>
       <c r="AC360" t="inlineStr"/>
       <c r="AD360" t="inlineStr"/>
-      <c r="AE360" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF360" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG360" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH360" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI360" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ360" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK360" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="AL360" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AM360" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="AN360" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AO360" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="AP360" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AQ360" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="AR360" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AS360" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AT360" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AU360" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV360" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AE360" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF360" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG360" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH360" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI360" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ360" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK360" t="n">
+        <v>242</v>
+      </c>
+      <c r="AL360" t="n">
+        <v>113</v>
+      </c>
+      <c r="AM360" t="n">
+        <v>214</v>
+      </c>
+      <c r="AN360" t="n">
+        <v>86</v>
+      </c>
+      <c r="AO360" t="n">
+        <v>94</v>
+      </c>
+      <c r="AP360" t="n">
+        <v>83</v>
+      </c>
+      <c r="AQ360" t="n">
+        <v>62</v>
+      </c>
+      <c r="AR360" t="n">
+        <v>54</v>
+      </c>
+      <c r="AS360" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT360" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU360" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV360" t="n">
+        <v>0</v>
       </c>
       <c r="AW360" t="inlineStr">
         <is>
@@ -78058,32 +77024,22 @@
       <c r="BC360" t="n">
         <v>0</v>
       </c>
-      <c r="BD360" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD360" t="n">
+        <v>2024</v>
       </c>
       <c r="BE360" t="inlineStr"/>
       <c r="BF360" t="inlineStr"/>
-      <c r="BG360" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BH360" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BI360" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ360" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="BG360" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH360" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI360" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ360" t="n">
+        <v>5</v>
       </c>
       <c r="BK360" t="inlineStr"/>
       <c r="BL360" t="inlineStr"/>
@@ -78121,15 +77077,11 @@
           <t>9 069</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G361" t="n">
+        <v>1</v>
+      </c>
+      <c r="H361" t="n">
+        <v>0</v>
       </c>
       <c r="I361" t="inlineStr">
         <is>
@@ -78161,159 +77113,99 @@
           <t>36%</t>
         </is>
       </c>
-      <c r="O361" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="P361" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q361" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R361" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S361" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T361" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U361" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V361" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="O361" t="n">
+        <v>14</v>
+      </c>
+      <c r="P361" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>8</v>
+      </c>
+      <c r="R361" t="n">
+        <v>1</v>
+      </c>
+      <c r="S361" t="n">
+        <v>4</v>
+      </c>
+      <c r="T361" t="n">
+        <v>2</v>
+      </c>
+      <c r="U361" t="n">
+        <v>2</v>
+      </c>
+      <c r="V361" t="n">
+        <v>5</v>
       </c>
       <c r="W361" t="inlineStr"/>
       <c r="X361" t="inlineStr"/>
-      <c r="Y361" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z361" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA361" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB361" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y361" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA361" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB361" t="n">
+        <v>1</v>
       </c>
       <c r="AC361" t="inlineStr"/>
       <c r="AD361" t="inlineStr"/>
-      <c r="AE361" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF361" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AG361" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH361" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AI361" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ361" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK361" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="AL361" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="AM361" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="AN361" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="AO361" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AP361" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AQ361" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AR361" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AS361" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AT361" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AU361" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AV361" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AE361" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF361" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG361" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH361" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI361" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ361" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK361" t="n">
+        <v>649</v>
+      </c>
+      <c r="AL361" t="n">
+        <v>378</v>
+      </c>
+      <c r="AM361" t="n">
+        <v>574</v>
+      </c>
+      <c r="AN361" t="n">
+        <v>322</v>
+      </c>
+      <c r="AO361" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP361" t="n">
+        <v>74</v>
+      </c>
+      <c r="AQ361" t="n">
+        <v>63</v>
+      </c>
+      <c r="AR361" t="n">
+        <v>37</v>
+      </c>
+      <c r="AS361" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT361" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU361" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV361" t="n">
+        <v>2</v>
       </c>
       <c r="AW361" t="inlineStr">
         <is>
@@ -78344,32 +77236,22 @@
       <c r="BC361" t="n">
         <v>0</v>
       </c>
-      <c r="BD361" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD361" t="n">
+        <v>2024</v>
       </c>
       <c r="BE361" t="inlineStr"/>
       <c r="BF361" t="inlineStr"/>
-      <c r="BG361" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BH361" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BI361" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BJ361" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="BG361" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH361" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI361" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ361" t="n">
+        <v>12</v>
       </c>
       <c r="BK361" t="inlineStr"/>
       <c r="BL361" t="inlineStr"/>
@@ -78407,15 +77289,11 @@
           <t>8 207</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G362" t="n">
+        <v>1</v>
+      </c>
+      <c r="H362" t="n">
+        <v>0</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
@@ -78447,159 +77325,99 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="O362" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P362" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Q362" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R362" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S362" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T362" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U362" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V362" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="O362" t="n">
+        <v>12</v>
+      </c>
+      <c r="P362" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>4</v>
+      </c>
+      <c r="R362" t="n">
+        <v>0</v>
+      </c>
+      <c r="S362" t="n">
+        <v>5</v>
+      </c>
+      <c r="T362" t="n">
+        <v>2</v>
+      </c>
+      <c r="U362" t="n">
+        <v>3</v>
+      </c>
+      <c r="V362" t="n">
+        <v>4</v>
       </c>
       <c r="W362" t="inlineStr"/>
       <c r="X362" t="inlineStr"/>
-      <c r="Y362" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z362" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA362" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB362" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y362" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA362" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB362" t="n">
+        <v>0</v>
       </c>
       <c r="AC362" t="inlineStr"/>
       <c r="AD362" t="inlineStr"/>
-      <c r="AE362" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF362" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG362" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AH362" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI362" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ362" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK362" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="AL362" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="AM362" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="AN362" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="AO362" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AP362" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="AQ362" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AR362" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AS362" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AT362" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AU362" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AV362" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AE362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF362" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG362" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH362" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI362" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK362" t="n">
+        <v>440</v>
+      </c>
+      <c r="AL362" t="n">
+        <v>512</v>
+      </c>
+      <c r="AM362" t="n">
+        <v>369</v>
+      </c>
+      <c r="AN362" t="n">
+        <v>432</v>
+      </c>
+      <c r="AO362" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP362" t="n">
+        <v>105</v>
+      </c>
+      <c r="AQ362" t="n">
+        <v>70</v>
+      </c>
+      <c r="AR362" t="n">
+        <v>49</v>
+      </c>
+      <c r="AS362" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT362" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU362" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV362" t="n">
+        <v>1</v>
       </c>
       <c r="AW362" t="inlineStr">
         <is>
@@ -78630,35 +77448,891 @@
       <c r="BC362" t="n">
         <v>0</v>
       </c>
-      <c r="BD362" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BD362" t="n">
+        <v>2024</v>
       </c>
       <c r="BE362" t="inlineStr"/>
       <c r="BF362" t="inlineStr"/>
-      <c r="BG362" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BH362" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BI362" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BJ362" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BG362" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH362" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI362" t="n">
+        <v>11</v>
+      </c>
+      <c r="BJ362" t="n">
+        <v>6</v>
       </c>
       <c r="BK362" t="inlineStr"/>
       <c r="BL362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>WdfLujx9</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>11.09.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Ndiaye A.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>ONEOK Field
+ (Tulsa, OK)</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>7 833</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>2 663</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>OEz4Fa6C</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>FC Tulsa</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr"/>
+      <c r="X363" t="inlineStr"/>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB363" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr"/>
+      <c r="AD363" t="inlineStr"/>
+      <c r="AE363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF363" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK363" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="AL363" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="AM363" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="AN363" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="AO363" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AP363" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AQ363" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AR363" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AT363" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AU363" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AV363" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW363" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="AX363" t="inlineStr">
+        <is>
+          <t>sanchez mario</t>
+        </is>
+      </c>
+      <c r="AY363" t="inlineStr">
+        <is>
+          <t>zDeq7OqE</t>
+        </is>
+      </c>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>sanchez dennis</t>
+        </is>
+      </c>
+      <c r="BA363" t="n">
+        <v>167</v>
+      </c>
+      <c r="BB363" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BC363" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD363" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BE363" t="inlineStr"/>
+      <c r="BF363" t="inlineStr"/>
+      <c r="BG363" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BH363" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BI363" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BJ363" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BK363" t="inlineStr"/>
+      <c r="BL363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>h6eHtWM2</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>11.09.2024 21:00</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Hernandez L.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Protective Stadium
+ (Birmingham, AL)</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>47 100</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>5 058</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>AohGC74A</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Tampa Bay</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr"/>
+      <c r="X364" t="inlineStr"/>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC364" t="inlineStr"/>
+      <c r="AD364" t="inlineStr"/>
+      <c r="AE364" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF364" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI364" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ364" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK364" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="AL364" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AM364" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="AN364" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="AO364" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AP364" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AQ364" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AR364" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AT364" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AU364" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AV364" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW364" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="AX364" t="inlineStr">
+        <is>
+          <t>soehn tom</t>
+        </is>
+      </c>
+      <c r="AY364" t="inlineStr">
+        <is>
+          <t>r7lXig46</t>
+        </is>
+      </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>law nicky</t>
+        </is>
+      </c>
+      <c r="BA364" t="n">
+        <v>167</v>
+      </c>
+      <c r="BB364" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BC364" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD364" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BE364" t="inlineStr"/>
+      <c r="BF364" t="inlineStr"/>
+      <c r="BG364" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BH364" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BI364" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ364" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK364" t="inlineStr"/>
+      <c r="BL364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>QJgPvAiF</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>11.09.2024 21:00</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Osmanovic E.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>AutoZone Park
+ (Memphis, TN)</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>3 013</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>MoS88xdH</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Ew2P6PKC</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr"/>
+      <c r="X365" t="inlineStr"/>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB365" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC365" t="inlineStr"/>
+      <c r="AD365" t="inlineStr"/>
+      <c r="AE365" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF365" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AI365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ365" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK365" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="AL365" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="AM365" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="AN365" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="AO365" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AP365" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AQ365" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AR365" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AS365" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AT365" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AU365" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW365" t="inlineStr">
+        <is>
+          <t>S2Oqee3l</t>
+        </is>
+      </c>
+      <c r="AX365" t="inlineStr">
+        <is>
+          <t>glass stephen</t>
+        </is>
+      </c>
+      <c r="AY365" t="inlineStr">
+        <is>
+          <t>xYHj0Fat</t>
+        </is>
+      </c>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>burke brendan</t>
+        </is>
+      </c>
+      <c r="BA365" t="n">
+        <v>167</v>
+      </c>
+      <c r="BB365" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BC365" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD365" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BE365" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG365" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BH365" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BI365" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ365" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BK365" t="inlineStr"/>
+      <c r="BL365" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
